--- a/results/RQ3/summary_period_category_tools.xlsx
+++ b/results/RQ3/summary_period_category_tools.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,34 +417,34 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>anually</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>annually</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>not applicable</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>3rd Party Vulnerability Scanning</t>
         </is>
@@ -498,7 +486,9 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>df not exists</t>
+          <t>Snyk: 1;
+PHP Security Checker: 1;
+Trivy: 1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -512,7 +502,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Static Application Security Testing</t>
         </is>
@@ -545,7 +535,9 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>df not exists</t>
+          <t>SonarQube: 1;
+CodeQL: 1;
+ESLint Security: 1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -557,7 +549,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Dynamic Application Security Testing</t>
         </is>
@@ -581,7 +573,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>df not exists</t>
+          <t>Checkmarx: 2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -592,7 +584,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Secure Configuration/Hardening</t>
         </is>
@@ -623,7 +615,9 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>df not exists</t>
+          <t>Terraform: 4;
+Ansible: 3;
+Phan: 1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -636,7 +630,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Compliance/Hardening Checks</t>
         </is>
@@ -657,7 +651,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>df not exists</t>
+          <t>Puppet-Lint: 1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -670,7 +664,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Secrets Management</t>
         </is>
@@ -699,7 +693,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>df not exists</t>
+          <t>GitLeaks: 2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
